--- a/docs/test-cases/SPM-23_Test_Cases.xlsx
+++ b/docs/test-cases/SPM-23_Test_Cases.xlsx
@@ -29,6 +29,20 @@
     <sheet name="TC19" sheetId="21" state="visible" r:id="rId21"/>
     <sheet name="TC20" sheetId="22" state="visible" r:id="rId22"/>
     <sheet name="TC21" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet name="TC22" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet name="TC23" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet name="TC24" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet name="TC25" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet name="TC26" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet name="TC27" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet name="TC28" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet name="TC29" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet name="TC30" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet name="TC31" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet name="TC32" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet name="TC33" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet name="TC34" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet name="TC35" sheetId="37" state="visible" r:id="rId37"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -468,7 +482,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -924,7 +938,7 @@
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
-          <t>Requesting the same equipment item twice is rejected</t>
+          <t>An equipment item already chosen in one row is not offered again in another row</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
@@ -934,7 +948,7 @@
       </c>
       <c r="E16" s="11" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="F16" s="11" t="inlineStr">
@@ -1089,7 +1103,7 @@
       </c>
       <c r="D21" s="11" t="inlineStr">
         <is>
-          <t>AC6</t>
+          <t>AC7</t>
         </is>
       </c>
       <c r="E21" s="11" t="inlineStr">
@@ -1121,7 +1135,7 @@
       </c>
       <c r="D22" s="11" t="inlineStr">
         <is>
-          <t>AC6</t>
+          <t>AC7</t>
         </is>
       </c>
       <c r="E22" s="11" t="inlineStr">
@@ -1153,7 +1167,7 @@
       </c>
       <c r="D23" s="11" t="inlineStr">
         <is>
-          <t>AC7</t>
+          <t>AC8</t>
         </is>
       </c>
       <c r="E23" s="11" t="inlineStr">
@@ -1185,7 +1199,7 @@
       </c>
       <c r="D24" s="11" t="inlineStr">
         <is>
-          <t>AC7</t>
+          <t>AC8</t>
         </is>
       </c>
       <c r="E24" s="11" t="inlineStr">
@@ -1199,125 +1213,573 @@
         </is>
       </c>
     </row>
+    <row r="25">
+      <c r="A25" s="10" t="inlineStr">
+        <is>
+          <t>TC22</t>
+        </is>
+      </c>
+      <c r="B25" s="11" t="inlineStr">
+        <is>
+          <t>SPM-23-TC22</t>
+        </is>
+      </c>
+      <c r="C25" s="11" t="inlineStr">
+        <is>
+          <t>Organiser can split an event into two sessions, each with its own start and end</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="inlineStr">
+        <is>
+          <t>AC6</t>
+        </is>
+      </c>
+      <c r="E25" s="11" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>Acceptance Criteria</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>TC23</t>
+        </is>
+      </c>
+      <c r="B26" s="11" t="inlineStr">
+        <is>
+          <t>SPM-23-TC23</t>
+        </is>
+      </c>
+      <c r="C26" s="11" t="inlineStr">
+        <is>
+          <t>Each session has its own expected attendance and preferred room layout</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="inlineStr">
+        <is>
+          <t>AC6</t>
+        </is>
+      </c>
+      <c r="E26" s="11" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>Acceptance Criteria</t>
+        </is>
+      </c>
+    </row>
     <row r="27">
-      <c r="A27" s="7" t="inlineStr">
+      <c r="A27" s="10" t="inlineStr">
+        <is>
+          <t>TC24</t>
+        </is>
+      </c>
+      <c r="B27" s="11" t="inlineStr">
+        <is>
+          <t>SPM-23-TC24</t>
+        </is>
+      </c>
+      <c r="C27" s="11" t="inlineStr">
+        <is>
+          <t>Each session can request its own equipment</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="inlineStr">
+        <is>
+          <t>AC6</t>
+        </is>
+      </c>
+      <c r="E27" s="11" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>Acceptance Criteria</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="10" t="inlineStr">
+        <is>
+          <t>TC25</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="inlineStr">
+        <is>
+          <t>SPM-23-TC25</t>
+        </is>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>Ticking "This event has multiple sessions" swaps the event-level sections for two sessions</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="inlineStr">
+        <is>
+          <t>AC6</t>
+        </is>
+      </c>
+      <c r="E28" s="11" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="10" t="inlineStr">
+        <is>
+          <t>TC26</t>
+        </is>
+      </c>
+      <c r="B29" s="11" t="inlineStr">
+        <is>
+          <t>SPM-23-TC26</t>
+        </is>
+      </c>
+      <c r="C29" s="11" t="inlineStr">
+        <is>
+          <t>Sessions can be changed on a saved draft, and switched off again</t>
+        </is>
+      </c>
+      <c r="D29" s="11" t="inlineStr">
+        <is>
+          <t>AC6</t>
+        </is>
+      </c>
+      <c r="E29" s="11" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F29" s="11" t="inlineStr">
+        <is>
+          <t>Acceptance Criteria</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="10" t="inlineStr">
+        <is>
+          <t>TC27</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="inlineStr">
+        <is>
+          <t>SPM-23-TC27</t>
+        </is>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>A multi-session draft is identifiable as a draft and shows the span and largest attendance</t>
+        </is>
+      </c>
+      <c r="D30" s="11" t="inlineStr">
+        <is>
+          <t>AC6, AC8</t>
+        </is>
+      </c>
+      <c r="E30" s="11" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F30" s="11" t="inlineStr">
+        <is>
+          <t>Acceptance Criteria</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="10" t="inlineStr">
+        <is>
+          <t>TC28</t>
+        </is>
+      </c>
+      <c r="B31" s="11" t="inlineStr">
+        <is>
+          <t>SPM-23-TC28</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>Venue and accessibility requirements apply to every session</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>AC5, AC6</t>
+        </is>
+      </c>
+      <c r="E31" s="11" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>TC29</t>
+        </is>
+      </c>
+      <c r="B32" s="11" t="inlineStr">
+        <is>
+          <t>SPM-23-TC29</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>An equipment item chosen in one session is not offered in another session</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="inlineStr">
+        <is>
+          <t>AC6</t>
+        </is>
+      </c>
+      <c r="E32" s="11" t="inlineStr">
+        <is>
+          <t>Boundary</t>
+        </is>
+      </c>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>TC30</t>
+        </is>
+      </c>
+      <c r="B33" s="11" t="inlineStr">
+        <is>
+          <t>SPM-23-TC30</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>Submit is blocked when a session is missing its required information</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="inlineStr">
+        <is>
+          <t>AC6, AC7</t>
+        </is>
+      </c>
+      <c r="E33" s="11" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>Acceptance Criteria</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="10" t="inlineStr">
+        <is>
+          <t>TC31</t>
+        </is>
+      </c>
+      <c r="B34" s="11" t="inlineStr">
+        <is>
+          <t>SPM-23-TC31</t>
+        </is>
+      </c>
+      <c r="C34" s="11" t="inlineStr">
+        <is>
+          <t>Invalid session values are each flagged on the session they belong to</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="inlineStr">
+        <is>
+          <t>AC6, AC7</t>
+        </is>
+      </c>
+      <c r="E34" s="11" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="F34" s="11" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="10" t="inlineStr">
+        <is>
+          <t>TC32</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="inlineStr">
+        <is>
+          <t>SPM-23-TC32</t>
+        </is>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>Registration must open before the FIRST session starts</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="inlineStr">
+        <is>
+          <t>AC5, AC6, AC7</t>
+        </is>
+      </c>
+      <c r="E35" s="11" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="10" t="inlineStr">
+        <is>
+          <t>TC33</t>
+        </is>
+      </c>
+      <c r="B36" s="11" t="inlineStr">
+        <is>
+          <t>SPM-23-TC33</t>
+        </is>
+      </c>
+      <c r="C36" s="11" t="inlineStr">
+        <is>
+          <t>A fully completed multi-session request can be submitted</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="inlineStr">
+        <is>
+          <t>AC6, AC7</t>
+        </is>
+      </c>
+      <c r="E36" s="11" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F36" s="11" t="inlineStr">
+        <is>
+          <t>Acceptance Criteria</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t>TC34</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="inlineStr">
+        <is>
+          <t>SPM-23-TC34</t>
+        </is>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>Saving a draft needs each session's times, but not attendance or type</t>
+        </is>
+      </c>
+      <c r="D37" s="11" t="inlineStr">
+        <is>
+          <t>AC6, AC8</t>
+        </is>
+      </c>
+      <c r="E37" s="11" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="F37" s="11" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="10" t="inlineStr">
+        <is>
+          <t>TC35</t>
+        </is>
+      </c>
+      <c r="B38" s="11" t="inlineStr">
+        <is>
+          <t>SPM-23-TC35</t>
+        </is>
+      </c>
+      <c r="C38" s="11" t="inlineStr">
+        <is>
+          <t>A normal single-session request is unchanged by the sessions option</t>
+        </is>
+      </c>
+      <c r="D38" s="11" t="inlineStr">
+        <is>
+          <t>AC6</t>
+        </is>
+      </c>
+      <c r="E38" s="11" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="F38" s="11" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="7" t="inlineStr">
         <is>
           <t>AC</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B41" s="7" t="inlineStr">
         <is>
           <t>Acceptance Criterion</t>
         </is>
       </c>
-      <c r="C27" s="8" t="n"/>
-      <c r="D27" s="9" t="n"/>
-      <c r="E27" s="7" t="inlineStr">
+      <c r="C41" s="8" t="n"/>
+      <c r="D41" s="9" t="n"/>
+      <c r="E41" s="7" t="inlineStr">
         <is>
           <t>Covered by</t>
         </is>
       </c>
-      <c r="F27" s="9" t="n"/>
-    </row>
-    <row r="28" ht="31" customHeight="1">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="F41" s="9" t="n"/>
+    </row>
+    <row r="42" ht="31" customHeight="1">
+      <c r="A42" s="11" t="inlineStr">
         <is>
           <t>AC1</t>
         </is>
       </c>
-      <c r="B28" s="11" t="inlineStr">
+      <c r="B42" s="11" t="inlineStr">
         <is>
           <t>The Event Organiser can enter an event name and purpose.</t>
         </is>
       </c>
-      <c r="C28" s="8" t="n"/>
-      <c r="D28" s="9" t="n"/>
-      <c r="E28" s="11" t="inlineStr">
+      <c r="C42" s="8" t="n"/>
+      <c r="D42" s="9" t="n"/>
+      <c r="E42" s="11" t="inlineStr">
         <is>
           <t>SPM-23-TC01
 SPM-23-TC02</t>
         </is>
       </c>
-      <c r="F28" s="9" t="n"/>
-    </row>
-    <row r="29" ht="17.5" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
+      <c r="F42" s="9" t="n"/>
+    </row>
+    <row r="43" ht="17.5" customHeight="1">
+      <c r="A43" s="11" t="inlineStr">
         <is>
           <t>AC2</t>
         </is>
       </c>
-      <c r="B29" s="11" t="inlineStr">
+      <c r="B43" s="11" t="inlineStr">
         <is>
           <t>The Event Organiser can enter an event description.</t>
         </is>
       </c>
-      <c r="C29" s="8" t="n"/>
-      <c r="D29" s="9" t="n"/>
-      <c r="E29" s="11" t="inlineStr">
+      <c r="C43" s="8" t="n"/>
+      <c r="D43" s="9" t="n"/>
+      <c r="E43" s="11" t="inlineStr">
         <is>
           <t>SPM-23-TC03</t>
         </is>
       </c>
-      <c r="F29" s="9" t="n"/>
-    </row>
-    <row r="30" ht="44.5" customHeight="1">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="F43" s="9" t="n"/>
+    </row>
+    <row r="44" ht="44.5" customHeight="1">
+      <c r="A44" s="11" t="inlineStr">
         <is>
           <t>AC3</t>
         </is>
       </c>
-      <c r="B30" s="11" t="inlineStr">
+      <c r="B44" s="11" t="inlineStr">
         <is>
           <t>The Event Organiser can specify the proposed date and time.</t>
         </is>
       </c>
-      <c r="C30" s="8" t="n"/>
-      <c r="D30" s="9" t="n"/>
-      <c r="E30" s="11" t="inlineStr">
+      <c r="C44" s="8" t="n"/>
+      <c r="D44" s="9" t="n"/>
+      <c r="E44" s="11" t="inlineStr">
         <is>
           <t>SPM-23-TC04
 SPM-23-TC05
 SPM-23-TC06</t>
         </is>
       </c>
-      <c r="F30" s="9" t="n"/>
-    </row>
-    <row r="31" ht="44.5" customHeight="1">
-      <c r="A31" s="11" t="inlineStr">
+      <c r="F44" s="9" t="n"/>
+    </row>
+    <row r="45" ht="44.5" customHeight="1">
+      <c r="A45" s="11" t="inlineStr">
         <is>
           <t>AC4</t>
         </is>
       </c>
-      <c r="B31" s="11" t="inlineStr">
+      <c r="B45" s="11" t="inlineStr">
         <is>
           <t>The Event Organiser can specify expected attendance.</t>
         </is>
       </c>
-      <c r="C31" s="8" t="n"/>
-      <c r="D31" s="9" t="n"/>
-      <c r="E31" s="11" t="inlineStr">
+      <c r="C45" s="8" t="n"/>
+      <c r="D45" s="9" t="n"/>
+      <c r="E45" s="11" t="inlineStr">
         <is>
           <t>SPM-23-TC07
 SPM-23-TC08
 SPM-23-TC09</t>
         </is>
       </c>
-      <c r="F31" s="9" t="n"/>
-    </row>
-    <row r="32" ht="112" customHeight="1">
-      <c r="A32" s="11" t="inlineStr">
+      <c r="F45" s="9" t="n"/>
+    </row>
+    <row r="46" ht="139" customHeight="1">
+      <c r="A46" s="11" t="inlineStr">
         <is>
           <t>AC5</t>
         </is>
       </c>
-      <c r="B32" s="11" t="inlineStr">
+      <c r="B46" s="11" t="inlineStr">
         <is>
           <t>The Event Organiser can specify venue, accessibility, equipment and registration requirements.</t>
         </is>
       </c>
-      <c r="C32" s="8" t="n"/>
-      <c r="D32" s="9" t="n"/>
-      <c r="E32" s="11" t="inlineStr">
+      <c r="C46" s="8" t="n"/>
+      <c r="D46" s="9" t="n"/>
+      <c r="E46" s="11" t="inlineStr">
         <is>
           <t>SPM-23-TC10
 SPM-23-TC11
@@ -1326,95 +1788,146 @@
 SPM-23-TC14
 SPM-23-TC15
 SPM-23-TC16
-SPM-23-TC17</t>
-        </is>
-      </c>
-      <c r="F32" s="9" t="n"/>
-    </row>
-    <row r="33" ht="31" customHeight="1">
-      <c r="A33" s="11" t="inlineStr">
+SPM-23-TC17
+SPM-23-TC28
+SPM-23-TC32</t>
+        </is>
+      </c>
+      <c r="F46" s="9" t="n"/>
+    </row>
+    <row r="47" ht="193" customHeight="1">
+      <c r="A47" s="11" t="inlineStr">
         <is>
           <t>AC6</t>
         </is>
       </c>
-      <c r="B33" s="11" t="inlineStr">
+      <c r="B47" s="11" t="inlineStr">
+        <is>
+          <t>An event can be organised into multiple sessions, each with its own timing, expected attendance, venue and equipment requirements (e.g. a multi-day conference with different rooms per day).</t>
+        </is>
+      </c>
+      <c r="C47" s="8" t="n"/>
+      <c r="D47" s="9" t="n"/>
+      <c r="E47" s="11" t="inlineStr">
+        <is>
+          <t>SPM-23-TC22
+SPM-23-TC23
+SPM-23-TC24
+SPM-23-TC25
+SPM-23-TC26
+SPM-23-TC27
+SPM-23-TC28
+SPM-23-TC29
+SPM-23-TC30
+SPM-23-TC31
+SPM-23-TC32
+SPM-23-TC33
+SPM-23-TC34
+SPM-23-TC35</t>
+        </is>
+      </c>
+      <c r="F47" s="9" t="n"/>
+    </row>
+    <row r="48" ht="85" customHeight="1">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
+          <t>AC7</t>
+        </is>
+      </c>
+      <c r="B48" s="11" t="inlineStr">
         <is>
           <t>The system validates required information before allowing submission.</t>
         </is>
       </c>
-      <c r="C33" s="8" t="n"/>
-      <c r="D33" s="9" t="n"/>
-      <c r="E33" s="11" t="inlineStr">
+      <c r="C48" s="8" t="n"/>
+      <c r="D48" s="9" t="n"/>
+      <c r="E48" s="11" t="inlineStr">
         <is>
           <t>SPM-23-TC18
-SPM-23-TC19</t>
-        </is>
-      </c>
-      <c r="F33" s="9" t="n"/>
-    </row>
-    <row r="34" ht="31" customHeight="1">
-      <c r="A34" s="11" t="inlineStr">
-        <is>
-          <t>AC7</t>
-        </is>
-      </c>
-      <c r="B34" s="11" t="inlineStr">
+SPM-23-TC19
+SPM-23-TC30
+SPM-23-TC31
+SPM-23-TC32
+SPM-23-TC33</t>
+        </is>
+      </c>
+      <c r="F48" s="9" t="n"/>
+    </row>
+    <row r="49" ht="58" customHeight="1">
+      <c r="A49" s="11" t="inlineStr">
+        <is>
+          <t>AC8</t>
+        </is>
+      </c>
+      <c r="B49" s="11" t="inlineStr">
         <is>
           <t>A newly created incomplete request is identifiable as a draft.</t>
         </is>
       </c>
-      <c r="C34" s="8" t="n"/>
-      <c r="D34" s="9" t="n"/>
-      <c r="E34" s="11" t="inlineStr">
+      <c r="C49" s="8" t="n"/>
+      <c r="D49" s="9" t="n"/>
+      <c r="E49" s="11" t="inlineStr">
         <is>
           <t>SPM-23-TC20
-SPM-23-TC21</t>
-        </is>
-      </c>
-      <c r="F34" s="9" t="n"/>
-    </row>
-    <row r="36" ht="98.5" customHeight="1">
-      <c r="A36" s="7" t="inlineStr">
+SPM-23-TC21
+SPM-23-TC27
+SPM-23-TC34</t>
+        </is>
+      </c>
+      <c r="F49" s="9" t="n"/>
+    </row>
+    <row r="51" ht="206.5" customHeight="1">
+      <c r="A51" s="7" t="inlineStr">
         <is>
           <t>Code reviewed</t>
         </is>
       </c>
-      <c r="B36" s="11" t="inlineStr">
-        <is>
-          <t>src/lib/validation.ts
+      <c r="B51" s="11" t="inlineStr">
+        <is>
+          <t>src/lib/validation/events.ts
 src/lib/eventForm.ts
+src/lib/eventSessions.ts
+src/lib/sessionWrites.ts
+src/components/SessionFields.tsx
 src/app/events/new/page.tsx
+src/app/events/[id]/edit/page.tsx
+src/app/events/page.tsx
 src/app/api/events/route.ts
 src/app/api/events/[id]/route.ts
 src/lib/__tests__/validation.test.ts
+src/lib/__tests__/eventForm.test.ts
+src/lib/__tests__/eventSessions.test.ts
+prisma/schema.prisma
 prisma/seed.ts</t>
         </is>
       </c>
-      <c r="C36" s="8" t="n"/>
-      <c r="D36" s="8" t="n"/>
-      <c r="E36" s="8" t="n"/>
-      <c r="F36" s="9" t="n"/>
+      <c r="C51" s="8" t="n"/>
+      <c r="D51" s="8" t="n"/>
+      <c r="E51" s="8" t="n"/>
+      <c r="F51" s="9" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
-    <mergeCell ref="B33:D33"/>
-    <mergeCell ref="B28:D28"/>
-    <mergeCell ref="E34:F34"/>
-    <mergeCell ref="E30:F30"/>
-    <mergeCell ref="E29:F29"/>
-    <mergeCell ref="B31:D31"/>
-    <mergeCell ref="E32:F32"/>
-    <mergeCell ref="B32:D32"/>
-    <mergeCell ref="E33:F33"/>
-    <mergeCell ref="E27:F27"/>
-    <mergeCell ref="B27:D27"/>
-    <mergeCell ref="E28:F28"/>
-    <mergeCell ref="B30:D30"/>
+  <mergeCells count="20">
+    <mergeCell ref="E43:F43"/>
+    <mergeCell ref="B42:D42"/>
+    <mergeCell ref="E42:F42"/>
+    <mergeCell ref="B44:D44"/>
+    <mergeCell ref="E48:F48"/>
+    <mergeCell ref="E44:F44"/>
+    <mergeCell ref="B49:D49"/>
     <mergeCell ref="B1:F1"/>
-    <mergeCell ref="B36:F36"/>
-    <mergeCell ref="B29:D29"/>
-    <mergeCell ref="E31:F31"/>
-    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="E47:F47"/>
+    <mergeCell ref="B45:D45"/>
+    <mergeCell ref="E46:F46"/>
+    <mergeCell ref="B41:D41"/>
+    <mergeCell ref="E49:F49"/>
+    <mergeCell ref="E45:F45"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="B46:D46"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="B51:F51"/>
+    <mergeCell ref="B43:D43"/>
+    <mergeCell ref="B48:D48"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A4" r:id="rId1"/>
@@ -1438,6 +1951,20 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId20"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A24" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A25" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A26" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A27" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A28" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A29" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A31" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A33" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A34" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A35" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A36" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A37" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A38" r:id="rId35"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -1544,7 +2071,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46281</v>
+        <v>46285</v>
       </c>
     </row>
     <row r="10">
@@ -1646,7 +2173,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="31" customHeight="1">
+    <row r="4" ht="44.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -1655,7 +2182,8 @@
       <c r="B4" s="13" t="inlineStr">
         <is>
           <t>1. Enter 1 into Expected attendance
-2. Click "Submit request"</t>
+2. Click "Submit request"
+3. Open the "My events" page</t>
         </is>
       </c>
     </row>
@@ -1671,7 +2199,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="31" customHeight="1">
+    <row r="6" ht="71.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -1679,7 +2207,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>The request is created and submitted. Its own page shows Expected attendance as 1.</t>
+          <t>No message appears under Expected attendance and the request is submitted. "My events" lists it under "Submitted" with status "Submitted" and Attendance 1. (After submitting, the browser is sent to the request's own page, which is not built yet and shows a 404 - ignore it and check "My events".)</t>
         </is>
       </c>
     </row>
@@ -1702,7 +2230,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46281</v>
+        <v>46285</v>
       </c>
     </row>
     <row r="10">
@@ -1792,7 +2320,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="44.5" customHeight="1">
+    <row r="3" ht="71.5" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -1800,11 +2328,11 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Logged in as rachel.ng@meridianfina.com / password123, on the "New event request" page, with Event name, Type, dates and attendance already filled in with valid values.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="44.5" customHeight="1">
+          <t>Logged in as rachel.ng@meridianfina.com / password123 (a seeded Event Organiser). Use your own initials in place of "KC" in every event name below so your drafts never clash with another tester's, on the "New event request" page, with Event name "Nusantara Product Launch 2026 - KC" filled in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="71.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -1814,11 +2342,12 @@
         <is>
           <t>1. Tick "High-density WiFi" under "The venue must have"
 2. Tick "Wheelchair spaces" under "Accessibility needs"
-3. Click "Submit request"</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="31" customHeight="1">
+3. Click "Save draft"
+4. From "My events", open the draft you just saved (find it by its name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44.5" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -1826,11 +2355,11 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Venue requirement: High-density WiFi; Accessibility need: Wheelchair spaces</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="31" customHeight="1">
+          <t>Event name: Nusantara Product Launch 2026 - KC; Venue requirement: High-density WiFi; Accessibility need: Wheelchair spaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -1838,7 +2367,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>The request is created. Its own page lists both "High-density WiFi" and "Wheelchair spaces" among its requirements.</t>
+          <t>The browser returns to "My events" and the draft is listed. Reopening it shows both "High-density WiFi" (under "The venue must have") and "Wheelchair spaces" (under "Accessibility needs") still ticked.</t>
         </is>
       </c>
     </row>
@@ -1861,7 +2390,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46281</v>
+        <v>46285</v>
       </c>
     </row>
     <row r="10">
@@ -1951,7 +2480,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="31" customHeight="1">
+    <row r="3" ht="112" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -1959,11 +2488,11 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>On the "New event request" page with Starts at = 5 Dec 2026, 9:00 AM and Ends at = 5 Dec 2026, 5:00 PM already set.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="58" customHeight="1">
+          <t>Logged in as rachel.ng@meridianfina.com / password123 (a seeded Event Organiser). Use your own initials in place of "KC" in every event name below so your drafts never clash with another tester's, on the "New event request" page, with Event name "Nusantara Product Launch 2026 - KC" filled in, and Starts at = 5 Dec 2026, 9:00 AM and Ends at = 5 Dec 2026, 5:00 PM already set. The equipment catalogue has at least two active items.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="85" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -1974,11 +2503,12 @@
           <t>1. Click "Add equipment"
 2. Choose "4K Portable Projector" in the Equipment list
 3. Enter 2 into Quantity
-4. Click "Submit request"</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="17.5" customHeight="1">
+4. Click "Save draft"
+5. From "My events", open the draft you just saved (find it by its name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="31" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -1986,11 +2516,11 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Equipment: 4K Portable Projector, quantity 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="31" customHeight="1">
+          <t>Event name: Nusantara Product Launch 2026 - KC; Equipment: 4K Portable Projector, quantity 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -1998,7 +2528,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>The request is created with "4K Portable Projector" (quantity 2) listed under its equipment.</t>
+          <t>The browser returns to "My events" and the draft is listed. Reopening it shows one equipment row with "4K Portable Projector" chosen and Quantity 2.</t>
         </is>
       </c>
     </row>
@@ -2021,7 +2551,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46281</v>
+        <v>46285</v>
       </c>
     </row>
     <row r="10">
@@ -2111,7 +2641,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="44.5" customHeight="1">
+    <row r="3" ht="71.5" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -2119,7 +2649,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Logged in as rachel.ng@meridianfina.com / password123, on the "New event request" page, with Starts at and Ends at left blank.</t>
+          <t>Logged in as rachel.ng@meridianfina.com / password123 (a seeded Event Organiser). Use your own initials in place of "KC" in every event name below so your drafts never clash with another tester's, on the "New event request" page, with Starts at and Ends at left blank.</t>
         </is>
       </c>
     </row>
@@ -2178,7 +2708,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46281</v>
+        <v>46285</v>
       </c>
     </row>
     <row r="10">
@@ -2268,7 +2798,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="31" customHeight="1">
+    <row r="3" ht="98.5" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -2276,11 +2806,11 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>On the "New event request" page with Starts at = 5 Dec 2026, 9:00 AM and Ends at = 5 Dec 2026, 5:00 PM already set.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="71.5" customHeight="1">
+          <t>Logged in as rachel.ng@meridianfina.com / password123 (a seeded Event Organiser). Use your own initials in place of "KC" in every event name below so your drafts never clash with another tester's, on the "New event request" page with Starts at = 5 Dec 2026, 9:00 AM and Ends at = 5 Dec 2026, 5:00 PM already set. The equipment catalogue has at least two active items.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="58" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -2288,13 +2818,13 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Add an equipment row, choose "4K Portable Projector", quantity 2
-2. Add a second equipment row, choose "4K Portable Projector" again, quantity 1
-3. Click "Submit request"</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="31" customHeight="1">
+          <t>1. Click "Add equipment" and choose "4K Portable Projector" in the first row
+2. Click "Add equipment" again to add a second row
+3. Open the second row's Equipment dropdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17.5" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -2302,11 +2832,11 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Equipment: "4K Portable Projector" selected in two separate rows</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44.5" customHeight="1">
+          <t>First row: 4K Portable Projector</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="71.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -2314,7 +2844,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>The page does not move on. A message "Each item can only be requested once — change the quantity instead of adding a second row." is shown above the equipment rows.</t>
+          <t>"4K Portable Projector" is not listed in the second row's dropdown - only items not already chosen elsewhere are offered, so the same item cannot be requested twice. Choosing a different item (for example "Lavalier Wireless Mic") in the second row and clicking "Save draft" saves both rows.</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2867,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46281</v>
+        <v>46285</v>
       </c>
     </row>
     <row r="10">
@@ -2427,7 +2957,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="31" customHeight="1">
+    <row r="3" ht="85" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -2435,11 +2965,11 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>On the "New event request" page with Starts at = 5 Dec 2026, 9:00 AM already set.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="71.5" customHeight="1">
+          <t>Logged in as rachel.ng@meridianfina.com / password123 (a seeded Event Organiser). Use your own initials in place of "KC" in every event name below so your drafts never clash with another tester's, on the "New event request" page, with Event name "Nusantara Product Launch 2026 - KC" filled in and Starts at = 5 Dec 2026, 9:00 AM already set.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="98.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -2451,11 +2981,12 @@
 2. Enter 300 into Registration capacity
 3. Set Registration opens to 1 Nov 2026, 12:00 AM
 4. Set Registration closes to 1 Dec 2026, 12:00 AM
-5. Click "Submit request"</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="31" customHeight="1">
+5. Click "Save draft"
+6. From "My events", open the draft you just saved (find it by its name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44.5" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -2463,11 +2994,11 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Registration capacity: 300; Registration opens: 1 Nov 2026, 12:00 AM; Registration closes: 1 Dec 2026, 12:00 AM</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="31" customHeight="1">
+          <t>Event name: Nusantara Product Launch 2026 - KC; Registration capacity: 300; Registration opens: 1 Nov 2026, 12:00 AM; Registration closes: 1 Dec 2026, 12:00 AM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="71.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -2475,7 +3006,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>The request is created with registration turned on, capacity 300, and the opens/closes dates shown exactly as entered.</t>
+          <t>The browser returns to "My events" and the draft is listed. Reopening it shows "Attendees need to register for this event" turned on, Registration capacity 300, Registration opens 1 Nov 2026, 12:00 AM and Registration closes 1 Dec 2026, 12:00 AM, exactly as entered.</t>
         </is>
       </c>
     </row>
@@ -2498,7 +3029,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46281</v>
+        <v>46285</v>
       </c>
     </row>
     <row r="10">
@@ -2657,7 +3188,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46281</v>
+        <v>46285</v>
       </c>
     </row>
     <row r="10">
@@ -2816,7 +3347,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46281</v>
+        <v>46285</v>
       </c>
     </row>
     <row r="10">
@@ -2974,7 +3505,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46281</v>
+        <v>46285</v>
       </c>
     </row>
     <row r="10">
@@ -3037,7 +3568,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -3062,16 +3593,60 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="17.5" customHeight="1">
+    <row r="2" ht="112" customHeight="1">
       <c r="A2" s="11" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="11" t="inlineStr">
         <is>
-          <t>None raised</t>
+          <t>Every case logs in as the seeded organiser rachel.ng@meridianfina.com, so all testers share one "My events" list (drafts are private per account, not per tester) alongside her seeded events. Each tester puts their initials in every event name so their own drafts can be told apart, and no case relies on any seeded event or draft. Two testers who use the same initials can still open each other's draft by mistake, and drafts cannot be deleted from the app, so repeat runs add duplicate rows.</t>
         </is>
       </c>
       <c r="C2" s="11" t="n"/>
+    </row>
+    <row r="3" ht="71.5" customHeight="1">
+      <c r="A3" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11" t="inlineStr">
+        <is>
+          <t>Cases that request equipment or tick facilities (TC10, TC11, TC13, TC24, TC28, TC29) need the seeded catalogue items ("4K Portable Projector", "Lavalier Wireless Mic", "High-density WiFi", "Wheelchair spaces") to exist. There is no screen to create equipment or facilities, so testers cannot set these up themselves. Accepted for now.</t>
+        </is>
+      </c>
+      <c r="C3" s="11" t="n"/>
+    </row>
+    <row r="4" ht="71.5" customHeight="1">
+      <c r="A4" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11" t="inlineStr">
+        <is>
+          <t>Cases that submit a request (TC04, TC07, TC09, TC18, TC33) end on the request's own page, which is not built yet and shows a 404 (Known Gaps, DOCUMENTATION.md; SPM-27/SPM-31). They check the result from "My events" instead. Once the detail page exists, these could also check what it shows.</t>
+        </is>
+      </c>
+      <c r="C4" s="11" t="n"/>
+    </row>
+    <row r="5" ht="85" customHeight="1">
+      <c r="A5" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11" t="inlineStr">
+        <is>
+          <t>Not written as manual cases because the UI cannot reach them: the server refusing a single-session list, refusing the same item in two sessions, and the submit-time check "Missing: session N expectedAttendance" (the form's own validation always stops these first). They are covered by unit tests in validation.test.ts, and were checked over HTTP during development.</t>
+        </is>
+      </c>
+      <c r="C5" s="11" t="n"/>
+    </row>
+    <row r="6" ht="98.5" customHeight="1">
+      <c r="A6" s="11" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11" t="inlineStr">
+        <is>
+          <t>SPM-23-TC13 was rewritten in this update: it still described a rejection message that can no longer appear (the equipment picker now hides already-chosen items, per the 2026-09-18 change). SPM-24-TC13 was fixed then; the SPM-23 copy was missed. TC10, TC11 and TC14 were also reworked to "Save draft, then reopen", because the details they checked were only visible on the unbuilt request page; TC11 and TC14 previously had no login or event name, so they could not have been run as written.</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3111,7 +3686,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="31" customHeight="1">
+    <row r="3" ht="58" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -3119,11 +3694,11 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Logged in as rachel.ng@meridianfina.com / password123, on the "New event request" page.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="85" customHeight="1">
+          <t>Logged in as rachel.ng@meridianfina.com / password123 (a seeded Event Organiser). Use your own initials in place of "KC" in every event name below so your drafts never clash with another tester's, on the "New event request" page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="112" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -3131,15 +3706,16 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Enter "Nusantara Product Launch 2026" into Event name
+          <t>1. Enter "Nusantara Product Launch 2026 - KC" into Event name
 2. Select "Exhibition" as Type of event
 3. Set Starts at to 5 Dec 2026, 9:00 AM and Ends at to 5 Dec 2026, 5:00 PM
 4. Enter 200 into Expected attendance
-5. Click "Submit request"</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="31" customHeight="1">
+5. Click "Submit request"
+6. Open the "My events" page</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44.5" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -3147,11 +3723,11 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Event name, Type, Starts at, Ends at and Expected attendance all valid, as above</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="31" customHeight="1">
+          <t>Event name: Nusantara Product Launch 2026 - KC; Type: Exhibition; Starts at: 5 Dec 2026, 9:00 AM; Ends at: 5 Dec 2026, 5:00 PM; Expected attendance: 200</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="85" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -3159,7 +3735,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>The browser moves to the request's own page, showing status "Submitted".</t>
+          <t>No message appears and the request is submitted. "My events" lists it under "Submitted" (not under Drafts) with status "Submitted", When "5 Dec 2026, 09:00–17:00" and Attendance 200. (After submitting, the browser is sent to the request's own page, which is not built yet and shows a 404 - ignore it and check "My events".)</t>
         </is>
       </c>
     </row>
@@ -3182,7 +3758,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46281</v>
+        <v>46285</v>
       </c>
     </row>
     <row r="10">
@@ -3272,7 +3848,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="31" customHeight="1">
+    <row r="3" ht="71.5" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -3280,11 +3856,11 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Logged in as rachel.ng@meridianfina.com / password123, on the "New event request" page, with only Event name filled in.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="58" customHeight="1">
+          <t>Logged in as rachel.ng@meridianfina.com / password123 (a seeded Event Organiser). Use your own initials in place of "KC" in every event name below so your drafts never clash with another tester's, on the "New event request" page, with only Event name filled in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="71.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -3292,7 +3868,7 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Enter "Nusantara Product Launch 2026" into Event name
+          <t>1. Enter "Nusantara Product Launch 2026 - KC" into Event name
 2. Leave Type of event, Starts at, Ends at, and Expected attendance empty
 3. Click "Submit request"</t>
         </is>
@@ -3341,7 +3917,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46281</v>
+        <v>46285</v>
       </c>
     </row>
     <row r="10">
@@ -3431,7 +4007,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="31" customHeight="1">
+    <row r="3" ht="58" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -3439,7 +4015,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Logged in as rachel.ng@meridianfina.com / password123, on the "New event request" page.</t>
+          <t>Logged in as rachel.ng@meridianfina.com / password123 (a seeded Event Organiser). Use your own initials in place of "KC" in every event name below so your drafts never clash with another tester's, on the "New event request" page.</t>
         </is>
       </c>
     </row>
@@ -3451,13 +4027,13 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Enter "Nusantara Product Launch 2026" into Event name only
+          <t>1. Enter "Nusantara Product Launch 2026 - KC" into Event name only
 2. Click "Save draft"
 3. Open the "My events" page</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="17.5" customHeight="1">
+    <row r="5" ht="31" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -3465,7 +4041,7 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Event name: Nusantara Product Launch 2026 (no other fields)</t>
+          <t>Event name: Nusantara Product Launch 2026 - KC (no other fields)</t>
         </is>
       </c>
     </row>
@@ -3500,7 +4076,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46281</v>
+        <v>46285</v>
       </c>
     </row>
     <row r="10">
@@ -3590,7 +4166,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="31" customHeight="1">
+    <row r="3" ht="58" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -3598,7 +4174,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Logged in as rachel.ng@meridianfina.com / password123, on the "New event request" page.</t>
+          <t>Logged in as rachel.ng@meridianfina.com / password123 (a seeded Event Organiser). Use your own initials in place of "KC" in every event name below so your drafts never clash with another tester's, on the "New event request" page.</t>
         </is>
       </c>
     </row>
@@ -3658,7 +4234,973 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46281</v>
+        <v>46285</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Date of Execution</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col width="24.77734375" customWidth="1" min="1" max="1"/>
+    <col width="56.77734375" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="17.5" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>SPM-23-TC22</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="85" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Pre-conditions</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Logged in as rachel.ng@meridianfina.com / password123 (a seeded Event Organiser). Use your own initials in place of "KC" in every event name below so your drafts never clash with another tester's, on the "New event request" page, with Event name "Nusantara Summit 2026 - KC" and Type of event "Conference" already filled in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="139" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>1. Tick "This event has multiple sessions"
+2. In Session 1, enter "Day 1 - Keynotes" into Session name, set Starts at to 5 Dec 2026, 9:00 AM and Ends at to 5 Dec 2026, 5:00 PM
+3. In Session 2, enter "Day 2 - Workshops" into Session name, set Starts at to 6 Dec 2026, 10:00 AM and Ends at to 6 Dec 2026, 4:00 PM
+4. Click "Save draft"
+5. From "My events", open the draft you just saved (find it by its name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44.5" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Event name: Nusantara Summit 2026 - KC; Session 1: Day 1 - Keynotes, 5 Dec 2026 9:00 AM - 5:00 PM; Session 2: Day 2 - Workshops, 6 Dec 2026 10:00 AM - 4:00 PM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>The browser returns to "My events" and the draft is listed. Reopening it shows "This event has multiple sessions" ticked, with Session 1 and Session 2 showing exactly the names and start/end times entered.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17.5" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>kchoongg</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Creation Date</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>46285</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Date of Execution</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col width="24.77734375" customWidth="1" min="1" max="1"/>
+    <col width="56.77734375" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="17.5" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>SPM-23-TC23</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="125.5" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Pre-conditions</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Logged in as rachel.ng@meridianfina.com / password123 (a seeded Event Organiser). Use your own initials in place of "KC" in every event name below so your drafts never clash with another tester's, on the "New event request" page, with Event name "Nusantara Summit 2026 - KC" and Type of event "Conference" already filled in, "This event has multiple sessions" ticked and both sessions' start and end times filled in (Session 1: 5 Dec 2026 9:00 AM - 5:00 PM, Session 2: 6 Dec 2026 9:00 AM - 5:00 PM).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="98.5" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>1. In Session 1, enter 300 into Expected attendance and choose "Theatre" as Preferred room layout
+2. In Session 2, enter 80 into Expected attendance and choose "Classroom" as Preferred room layout
+3. Click "Save draft"
+4. From "My events", open the draft you just saved (find it by its name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="31" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Event name: Nusantara Summit 2026 - KC; Session 1: 300 attendees, Theatre; Session 2: 80 attendees, Classroom</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Reopening the draft shows Session 1 with Expected attendance 300 and layout "Theatre", and Session 2 with Expected attendance 80 and layout "Classroom" - the two sessions keep separate values.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17.5" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>kchoongg</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Creation Date</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>46285</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Date of Execution</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col width="24.77734375" customWidth="1" min="1" max="1"/>
+    <col width="56.77734375" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="17.5" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>SPM-23-TC24</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="112" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Pre-conditions</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Logged in as rachel.ng@meridianfina.com / password123 (a seeded Event Organiser). Use your own initials in place of "KC" in every event name below so your drafts never clash with another tester's, on the "New event request" page, with Event name "Nusantara Summit 2026 - KC" and Type of event "Conference" already filled in, "This event has multiple sessions" ticked and both sessions' start and end times filled in. The equipment catalogue has at least two active items.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="112" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>1. In Session 1, click "Add equipment", choose "4K Portable Projector" and enter 2 into Quantity
+2. In Session 2, click "Add equipment", choose "Lavalier Wireless Mic", enter 4 into Quantity and enter "Lapel only, no handheld" into Technical requirements
+3. Click "Save draft"
+4. From "My events", open the draft you just saved (find it by its name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44.5" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Event name: Nusantara Summit 2026 - KC; Session 1: 4K Portable Projector x2; Session 2: Lavalier Wireless Mic x4, "Lapel only, no handheld"</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Reopening the draft shows the projector (quantity 2) under Session 1 only, and the microphone (quantity 4, with the technical requirement text) under Session 2 only. Neither session shows the other's item.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17.5" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>kchoongg</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Creation Date</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>46285</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Date of Execution</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col width="24.77734375" customWidth="1" min="1" max="1"/>
+    <col width="56.77734375" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="17.5" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>SPM-23-TC25</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="112" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Pre-conditions</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Logged in as rachel.ng@meridianfina.com / password123 (a seeded Event Organiser). Use your own initials in place of "KC" in every event name below so your drafts never clash with another tester's, on the "New event request" page, with Event name "Nusantara Summit 2026 - KC" filled in, and Starts at = 5 Dec 2026, 9:00 AM, Ends at = 5 Dec 2026, 5:00 PM, Expected attendance = 300 already entered in the normal Schedule and Attendance sections.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="85" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>1. Tick "This event has multiple sessions"
+2. Scroll down the form
+3. Look at the "Remove session" buttons on Session 1 and Session 2
+4. Click "Add session"
+5. Click "Remove session" on Session 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="31" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Starts at 5 Dec 2026 9:00 AM; Ends at 5 Dec 2026 5:00 PM; Expected attendance 300</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="125.5" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>Two session cards, "Session 1" and "Session 2", appear. The Schedule, Attendance and event-level Equipment sections are no longer shown. Session 1 is already filled with Starts at 5 Dec 2026 9:00 AM, Ends at 5 Dec 2026 5:00 PM and Expected attendance 300 (nothing typed earlier is lost); Session 2 is blank. With two sessions both "Remove session" buttons are disabled; "Add session" adds a Session 3 and enables them; removing Session 3 returns to two sessions with the buttons disabled again.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17.5" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>kchoongg</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Creation Date</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>46285</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Date of Execution</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col width="24.77734375" customWidth="1" min="1" max="1"/>
+    <col width="56.77734375" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="17.5" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>SPM-23-TC26</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="85" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Pre-conditions</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Logged in as rachel.ng@meridianfina.com / password123 (a seeded Event Organiser). Use your own initials in place of "KC" in every event name below so your drafts never clash with another tester's, on the "New event request" page, with Event name "Nusantara Summit 2026 - KC" and Type of event "Conference" already filled in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="206.5" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>1. Tick "This event has multiple sessions"
+2. Set Session 1 to 5 Dec 2026, 9:00 AM - 5:00 PM with Expected attendance 300, and Session 2 to 6 Dec 2026, 9:00 AM - 5:00 PM with Expected attendance 80
+3. Click "Save draft"
+4. From "My events", open the draft you just saved (find it by its name)
+5. In Session 2, change Expected attendance from 80 to 120
+6. Click "Save draft"
+7. From "My events", open the draft you just saved (find it by its name)
+8. Untick "This event has multiple sessions"
+9. Click "Save draft"
+10. From "My events", open the draft you just saved (find it by its name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="31" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Event name: Nusantara Summit 2026 - KC; Session 2 Expected attendance: 80 -&gt; 120</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="98.5" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>First reopen: both sessions as entered. Second reopen: Session 2 shows Expected attendance 120 and everything else is unchanged. After unticking, the normal Schedule section returns showing Starts at 5 Dec 2026, 9:00 AM and Ends at 6 Dec 2026, 5:00 PM (the whole span); on the final reopen "This event has multiple sessions" is unticked and no session cards are shown.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17.5" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>kchoongg</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Creation Date</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>46285</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Date of Execution</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col width="24.77734375" customWidth="1" min="1" max="1"/>
+    <col width="56.77734375" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="17.5" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>SPM-23-TC27</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="125.5" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Pre-conditions</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Logged in as rachel.ng@meridianfina.com / password123 (a seeded Event Organiser). Use your own initials in place of "KC" in every event name below so your drafts never clash with another tester's, on the "New event request" page, with Event name "Nusantara Summit 2026 - KC" and Type of event "Conference" already filled in, "This event has multiple sessions" ticked, Session 1 = 5 Dec 2026 9:00 AM - 5:00 PM (300 attendees) and Session 2 = 6 Dec 2026 9:00 AM - 5:00 PM (80 attendees).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="31" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>1. Click "Save draft"
+2. Look at the new draft's row in "My events"</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="31" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Event name: Nusantara Summit 2026 - KC; Session 1: 300 attendees; Session 2: 80 attendees</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="71.5" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>The event appears under "Drafts - not yet submitted" with a "Draft" status badge, visually distinct from submitted requests. Its When column shows "5 Dec 2026, 09:00 – 6 Dec 2026, 17:00" (first session start to last session end) and Attendance shows 300 (the largest single session, not 380).</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17.5" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>kchoongg</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Creation Date</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>46285</v>
       </c>
     </row>
     <row r="10">
@@ -3748,7 +5290,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="31" customHeight="1">
+    <row r="3" ht="58" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -3756,7 +5298,327 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Logged in as Rachel Ng (rachel.ng@meridianfina.com / password123), a seeded Organiser. On the "New event request" page.</t>
+          <t>Logged in as rachel.ng@meridianfina.com / password123 (a seeded Event Organiser). Use your own initials in place of "KC" in every event name below so your drafts never clash with another tester's. On the "New event request" page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="71.5" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>1. Enter "Nusantara Product Launch 2026 - KC" into Event name
+2. Enter "Regional product launch and press event" into Purpose
+3. Click "Save draft"</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="31" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Event name: Nusantara Product Launch 2026 - KC; Purpose: Regional product launch and press event</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>The browser returns to "My events".
+The new draft appears with the title "Nusantara Product Launch 2026 - KC". Reopening it shows Purpose still filled in as "Regional product launch and press event".</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17.5" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>kchoongg</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Creation Date</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>46285</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Date of Execution</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col width="24.77734375" customWidth="1" min="1" max="1"/>
+    <col width="56.77734375" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="17.5" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>SPM-23-TC28</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="98.5" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Pre-conditions</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Logged in as rachel.ng@meridianfina.com / password123 (a seeded Event Organiser). Use your own initials in place of "KC" in every event name below so your drafts never clash with another tester's, on the "New event request" page, with Event name "Nusantara Summit 2026 - KC" and Type of event "Conference" already filled in and "This event has multiple sessions" ticked and both sessions' start and end times filled in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="85" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>1. Look under the "Venue requirements" heading
+2. Tick "High-density WiFi" under "The venue must have" and "Wheelchair spaces" under "Accessibility needs"
+3. Click "Save draft"
+4. From "My events", open the draft you just saved (find it by its name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="31" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Event name: Nusantara Summit 2026 - KC; Venue requirement: High-density WiFi; Accessibility need: Wheelchair spaces</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="44.5" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>The text "These apply to every session." is shown under the Venue requirements heading (there is no per-session facility list). After reopening, both boxes are still ticked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17.5" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>kchoongg</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Creation Date</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>46285</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Date of Execution</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col width="24.77734375" customWidth="1" min="1" max="1"/>
+    <col width="56.77734375" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="17.5" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>SPM-23-TC29</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="112" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Pre-conditions</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Logged in as rachel.ng@meridianfina.com / password123 (a seeded Event Organiser). Use your own initials in place of "KC" in every event name below so your drafts never clash with another tester's, on the "New event request" page, with Event name "Nusantara Summit 2026 - KC" and Type of event "Conference" already filled in, "This event has multiple sessions" ticked and both sessions' start and end times filled in. The equipment catalogue has at least two active items.</t>
         </is>
       </c>
     </row>
@@ -3768,9 +5630,326 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Enter "Nusantara Product Launch 2026" into Event name
-2. Enter "Regional product launch and press event" into Purpose
-3. Click "Save draft"</t>
+          <t>1. In Session 1, click "Add equipment" and choose "4K Portable Projector"
+2. In Session 2, click "Add equipment"
+3. Open Session 2's Equipment dropdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17.5" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Session 1: 4K Portable Projector</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>"4K Portable Projector" is not listed in Session 2's dropdown, although other items (for example "Lavalier Wireless Mic") are. An item can be requested once for the whole event; the note under "Equipment for this session" says so.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17.5" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>kchoongg</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Creation Date</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>46285</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Date of Execution</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col width="24.77734375" customWidth="1" min="1" max="1"/>
+    <col width="56.77734375" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="17.5" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>SPM-23-TC30</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="112" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Pre-conditions</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Logged in as rachel.ng@meridianfina.com / password123 (a seeded Event Organiser). Use your own initials in place of "KC" in every event name below so your drafts never clash with another tester's, on the "New event request" page, with Event name "Nusantara Summit 2026 - KC" and Type of event "Conference" already filled in, "This event has multiple sessions" ticked, Session 1 fully filled in (5 Dec 2026 9:00 AM - 5:00 PM, 300 attendees) and Session 2 left completely blank.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="17.5" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>1. Click "Submit request"</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="17.5" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Session 1 complete; Session 2 blank</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="85" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>The page does not move on. Under Session 2 only, messages appear: "Enter when this session starts." under Starts at, "Enter when this session ends." under Ends at, and "Enter how many people you expect." under Expected attendance. Session 1 shows no messages, and the cursor moves to Session 2's Starts at.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17.5" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>kchoongg</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Creation Date</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>46285</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Date of Execution</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col width="24.77734375" customWidth="1" min="1" max="1"/>
+    <col width="56.77734375" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="17.5" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>SPM-23-TC31</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="98.5" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Pre-conditions</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Logged in as rachel.ng@meridianfina.com / password123 (a seeded Event Organiser). Use your own initials in place of "KC" in every event name below so your drafts never clash with another tester's, on the "New event request" page, with Event name "Nusantara Summit 2026 - KC" and Type of event "Conference" already filled in and "This event has multiple sessions" ticked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="112" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>1. In Session 1, set Starts at to 1 Jan 2020, 9:00 AM, Ends at to 1 Jan 2020, 5:00 PM and enter 0 into Expected attendance
+2. In Session 2, set Starts at to 6 Dec 2026, 5:00 PM, Ends at to 6 Dec 2026, 9:00 AM (earlier than Starts at) and enter 80 into Expected attendance
+3. Click "Submit request"
+4. In Session 2, change Ends at to 6 Dec 2026, 6:00 PM</t>
         </is>
       </c>
     </row>
@@ -3782,7 +5961,167 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Event name: Nusantara Product Launch 2026; Purpose: Regional product launch and press event</t>
+          <t>Session 1: 1 Jan 2020 9:00 AM - 5:00 PM, attendance 0; Session 2: 6 Dec 2026 5:00 PM - 9:00 AM, attendance 80</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="85" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>The page does not move on. Session 1 shows "The start date is in the past." under Starts at and "Enter a whole number of people, at least 1." under Expected attendance. Session 2 shows "Ends at must be after starts at." under Ends at. Changing Session 2's Ends at to 6:00 PM removes that message straight away.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17.5" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>kchoongg</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Creation Date</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>46285</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Date of Execution</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col width="24.77734375" customWidth="1" min="1" max="1"/>
+    <col width="56.77734375" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="17.5" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>SPM-23-TC32</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="125.5" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Pre-conditions</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Logged in as rachel.ng@meridianfina.com / password123 (a seeded Event Organiser). Use your own initials in place of "KC" in every event name below so your drafts never clash with another tester's, on the "New event request" page, with Event name "Nusantara Summit 2026 - KC" and Type of event "Conference" already filled in, "This event has multiple sessions" ticked, Session 1 = 5 Dec 2026 9:00 AM - 5:00 PM (300 attendees) and Session 2 = 6 Dec 2026 9:00 AM - 5:00 PM (80 attendees).</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="71.5" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>1. Turn on "Attendees need to register for this event"
+2. Enter 300 into Registration capacity
+3. Set Registration opens to 5 Dec 2026, 12:00 PM (after Session 1 has started but before Session 2)
+4. Click "Submit request"</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="31" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Registration opens: 5 Dec 2026 12:00 PM; first session starts 5 Dec 2026 9:00 AM</t>
         </is>
       </c>
     </row>
@@ -3794,8 +6133,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>The browser returns to "My events".
-The new draft appears with the title "Nusantara Product Launch 2026". Reopening it shows Purpose still filled in as "Regional product launch and press event".</t>
+          <t>The page does not move on. "Registration must open before the event starts." appears under Registration opens. Changing Registration opens to 1 Nov 2026, 12:00 AM removes the message on the next submit.</t>
         </is>
       </c>
     </row>
@@ -3818,7 +6156,490 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46281</v>
+        <v>46285</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Date of Execution</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col width="24.77734375" customWidth="1" min="1" max="1"/>
+    <col width="56.77734375" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="17.5" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>SPM-23-TC33</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="85" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Pre-conditions</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Logged in as rachel.ng@meridianfina.com / password123 (a seeded Event Organiser). Use your own initials in place of "KC" in every event name below so your drafts never clash with another tester's, on the "New event request" page, with Event name "Nusantara Summit 2026 - KC" and Type of event "Conference" already filled in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="98.5" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>1. Tick "This event has multiple sessions"
+2. Fill Session 1 with Starts at 5 Dec 2026, 9:00 AM, Ends at 5 Dec 2026, 5:00 PM, Expected attendance 300
+3. Fill Session 2 with Starts at 6 Dec 2026, 9:00 AM, Ends at 6 Dec 2026, 5:00 PM, Expected attendance 1 (the minimum)
+4. Click "Submit request"
+5. Open the "My events" page</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="44.5" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Event name: Nusantara Summit 2026 - KC; Session 1: 5 Dec 2026 9:00 AM - 5:00 PM, 300; Session 2: 6 Dec 2026 9:00 AM - 5:00 PM, 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="85" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>No messages appear and the request is submitted: "My events" lists it under "Submitted" (not under Drafts) with status "Submitted", When "5 Dec 2026, 09:00 – 6 Dec 2026, 17:00" and Attendance 300. (The browser is then sent to the request's own page, which is not built yet and shows a 404 - see open questions - so check the result from "My events".)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17.5" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>kchoongg</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Creation Date</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>46285</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Date of Execution</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet36.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col width="24.77734375" customWidth="1" min="1" max="1"/>
+    <col width="56.77734375" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="17.5" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>SPM-23-TC34</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="85" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Pre-conditions</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Logged in as rachel.ng@meridianfina.com / password123 (a seeded Event Organiser). Use your own initials in place of "KC" in every event name below so your drafts never clash with another tester's, on the "New event request" page, with Event name "Nusantara Summit 2026 - KC" filled in and Type of event left unselected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="98.5" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>1. Tick "This event has multiple sessions"
+2. Set Session 1 to 5 Dec 2026, 9:00 AM - 5:00 PM and leave Session 2 completely blank; leave both Expected attendance fields empty
+3. Click "Save draft"
+4. Set Session 2 to 6 Dec 2026, 9:00 AM - 5:00 PM
+5. Click "Save draft"</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="31" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Event name: Nusantara Summit 2026 - KC; attendance and type left empty</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="85" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>First "Save draft": the page does not move on and "Enter when this session starts." / "Enter when this session ends." appear under Session 2 only (a session cannot be saved without its times). Second "Save draft": the browser returns to "My events" and the draft is listed with a "Draft" badge, even though attendance and type are empty.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17.5" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>kchoongg</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Creation Date</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>46285</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n"/>
+      <c r="C10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>Pass/Fail/Not Executed/Blocked</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Remarks</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>Executed by</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>Date of Execution</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet37.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1"/>
+  <cols>
+    <col width="24.77734375" customWidth="1" min="1" max="1"/>
+    <col width="56.77734375" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Item</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+    </row>
+    <row r="2" ht="17.5" customHeight="1">
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>Test Case ID</t>
+        </is>
+      </c>
+      <c r="B2" s="13" t="inlineStr">
+        <is>
+          <t>SPM-23-TC35</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="58" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>Pre-conditions</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>Logged in as rachel.ng@meridianfina.com / password123 (a seeded Event Organiser). Use your own initials in place of "KC" in every event name below so your drafts never clash with another tester's, on the "New event request" page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="125.5" customHeight="1">
+      <c r="A4" s="12" t="inlineStr">
+        <is>
+          <t>Test Steps</t>
+        </is>
+      </c>
+      <c r="B4" s="13" t="inlineStr">
+        <is>
+          <t>1. Look at the "Sessions" section and leave "This event has multiple sessions" unticked
+2. Enter "Nusantara Product Launch 2026 - KC" into Event name
+3. Set Starts at to 5 Dec 2026, 9:00 AM, Ends at to 5 Dec 2026, 5:00 PM and Expected attendance to 200
+4. Click "Save draft"
+5. From "My events", open the draft you just saved (find it by its name)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="31" customHeight="1">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>Test Data</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>Event name: Nusantara Product Launch 2026 - KC; one session: 5 Dec 2026 9:00 AM - 5:00 PM, 200 attendees</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>Expected Result</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>"This event has multiple sessions" is unticked by default and no session cards are shown; the normal Schedule and Attendance sections are used. Reopening the draft shows the same values and "This event has multiple sessions" still unticked.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="17.5" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>Created By</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>kchoongg</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>Creation Date</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="n">
+        <v>46285</v>
       </c>
     </row>
     <row r="10">
@@ -3908,7 +6729,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="31" customHeight="1">
+    <row r="3" ht="58" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -3916,7 +6737,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Logged in as rachel.ng@meridianfina.com / password123, on the "New event request" page.</t>
+          <t>Logged in as rachel.ng@meridianfina.com / password123 (a seeded Event Organiser). Use your own initials in place of "KC" in every event name below so your drafts never clash with another tester's, on the "New event request" page.</t>
         </is>
       </c>
     </row>
@@ -3977,7 +6798,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46281</v>
+        <v>46285</v>
       </c>
     </row>
     <row r="10">
@@ -4067,7 +6888,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="31" customHeight="1">
+    <row r="3" ht="58" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -4075,11 +6896,11 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Logged in as rachel.ng@meridianfina.com / password123, on the "New event request" page.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="71.5" customHeight="1">
+          <t>Logged in as rachel.ng@meridianfina.com / password123 (a seeded Event Organiser). Use your own initials in place of "KC" in every event name below so your drafts never clash with another tester's, on the "New event request" page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="85" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -4087,7 +6908,7 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>1. Enter "Nusantara Product Launch 2026" into Event name
+          <t>1. Enter "Nusantara Product Launch 2026 - KC" into Event name
 2. Enter "Press event with livestream and product demonstration area." into Description
 3. Click "Save draft"
 4. From "My events", open the draft again</t>
@@ -4137,7 +6958,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46281</v>
+        <v>46285</v>
       </c>
     </row>
     <row r="10">
@@ -4227,7 +7048,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="58" customHeight="1">
+    <row r="3" ht="85" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -4235,11 +7056,11 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Logged in as rachel.ng@meridianfina.com / password123, on the "New event request" page, with Event name "Nusantara Product Launch 2026", Type of event "Exhibition", and Expected attendance 200 already filled in.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="44.5" customHeight="1">
+          <t>Logged in as rachel.ng@meridianfina.com / password123 (a seeded Event Organiser). Use your own initials in place of "KC" in every event name below so your drafts never clash with another tester's, on the "New event request" page, with Event name "Nusantara Product Launch 2026 - KC", Type of event "Exhibition", and Expected attendance 200 already filled in.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="58" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -4249,11 +7070,12 @@
         <is>
           <t>1. Set Starts at to 5 Dec 2026, 9:00 AM
 2. Set Ends at to 5 Dec 2026, 5:00 PM
-3. Click "Submit request"</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="17.5" customHeight="1">
+3. Click "Submit request"
+4. Open the "My events" page</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="31" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
         <is>
           <t>Test Data</t>
@@ -4261,11 +7083,11 @@
       </c>
       <c r="B5" s="13" t="inlineStr">
         <is>
-          <t>Starts at: 5 Dec 2026, 9:00 AM; Ends at: 5 Dec 2026, 5:00 PM</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="44.5" customHeight="1">
+          <t>Event name: Nusantara Product Launch 2026 - KC; Starts at: 5 Dec 2026, 9:00 AM; Ends at: 5 Dec 2026, 5:00 PM</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="85" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -4273,7 +7095,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>The request is created and immediately submitted. Its own page shows Starts at 5 Dec 2026, 9:00 AM, Ends at 5 Dec 2026, 5:00 PM, and status "Submitted".</t>
+          <t>No message appears and the request is submitted. "My events" lists it under "Submitted" (not under Drafts) with status "Submitted" and When "5 Dec 2026, 09:00–17:00". (After submitting, the browser is sent to the request's own page, which is not built yet and shows a 404 - ignore it and check "My events".)</t>
         </is>
       </c>
     </row>
@@ -4296,7 +7118,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46281</v>
+        <v>46285</v>
       </c>
     </row>
     <row r="10">
@@ -4386,7 +7208,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="44.5" customHeight="1">
+    <row r="3" ht="85" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -4394,7 +7216,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Logged in as rachel.ng@meridianfina.com / password123, on the "New event request" page, with Event name, Type of event and Expected attendance already filled in with valid values.</t>
+          <t>Logged in as rachel.ng@meridianfina.com / password123 (a seeded Event Organiser). Use your own initials in place of "KC" in every event name below so your drafts never clash with another tester's, on the "New event request" page, with Event name, Type of event and Expected attendance already filled in with valid values.</t>
         </is>
       </c>
     </row>
@@ -4455,7 +7277,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46281</v>
+        <v>46285</v>
       </c>
     </row>
     <row r="10">
@@ -4545,7 +7367,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="44.5" customHeight="1">
+    <row r="3" ht="85" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -4553,7 +7375,7 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Logged in as rachel.ng@meridianfina.com / password123, on the "New event request" page, with Event name, Type of event and Expected attendance already filled in with valid values.</t>
+          <t>Logged in as rachel.ng@meridianfina.com / password123 (a seeded Event Organiser). Use your own initials in place of "KC" in every event name below so your drafts never clash with another tester's, on the "New event request" page, with Event name, Type of event and Expected attendance already filled in with valid values.</t>
         </is>
       </c>
     </row>
@@ -4614,7 +7436,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46281</v>
+        <v>46285</v>
       </c>
     </row>
     <row r="10">
@@ -4704,7 +7526,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="44.5" customHeight="1">
+    <row r="3" ht="85" customHeight="1">
       <c r="A3" s="12" t="inlineStr">
         <is>
           <t>Pre-conditions</t>
@@ -4712,11 +7534,11 @@
       </c>
       <c r="B3" s="13" t="inlineStr">
         <is>
-          <t>Logged in as rachel.ng@meridianfina.com / password123, on the "New event request" page, with Event name, Type of event, Starts at and Ends at already filled in with valid values.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="31" customHeight="1">
+          <t>Logged in as rachel.ng@meridianfina.com / password123 (a seeded Event Organiser). Use your own initials in place of "KC" in every event name below so your drafts never clash with another tester's, on the "New event request" page, with Event name, Type of event, Starts at and Ends at already filled in with valid values.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="44.5" customHeight="1">
       <c r="A4" s="12" t="inlineStr">
         <is>
           <t>Test Steps</t>
@@ -4725,7 +7547,8 @@
       <c r="B4" s="13" t="inlineStr">
         <is>
           <t>1. Enter 250 into Expected attendance
-2. Click "Submit request"</t>
+2. Click "Submit request"
+3. Open the "My events" page</t>
         </is>
       </c>
     </row>
@@ -4741,7 +7564,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="31" customHeight="1">
+    <row r="6" ht="71.5" customHeight="1">
       <c r="A6" s="12" t="inlineStr">
         <is>
           <t>Expected Result</t>
@@ -4749,7 +7572,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>The request is created and submitted. Its own page shows Expected attendance as 250.</t>
+          <t>No message appears and the request is submitted. "My events" lists it under "Submitted" with status "Submitted" and Attendance 250. (After submitting, the browser is sent to the request's own page, which is not built yet and shows a 404 - ignore it and check "My events".)</t>
         </is>
       </c>
     </row>
@@ -4772,7 +7595,7 @@
         </is>
       </c>
       <c r="B8" s="14" t="n">
-        <v>46281</v>
+        <v>46285</v>
       </c>
     </row>
     <row r="10">
